--- a/public/templates/综合题型.xlsx
+++ b/public/templates/综合题型.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,9 +431,12 @@
         <v>标签</v>
       </c>
       <c r="K1" t="str">
+        <v>领域</v>
+      </c>
+      <c r="L1" t="str">
         <v>选项E</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>选项F</v>
       </c>
     </row>
@@ -468,6 +471,9 @@
       <c r="J2" t="str">
         <v>部署</v>
       </c>
+      <c r="K2" t="str">
+        <v>部署</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -501,9 +507,12 @@
         <v>题型</v>
       </c>
       <c r="K3" t="str">
+        <v>题型</v>
+      </c>
+      <c r="L3" t="str">
         <v>简答</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v/>
       </c>
     </row>
@@ -538,6 +547,9 @@
       <c r="J4" t="str">
         <v>媒体</v>
       </c>
+      <c r="K4" t="str">
+        <v>媒体</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -570,6 +582,9 @@
       <c r="J5" t="str">
         <v>技术栈</v>
       </c>
+      <c r="K5" t="str">
+        <v>技术栈</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -602,10 +617,13 @@
       <c r="J6" t="str">
         <v>练习</v>
       </c>
+      <c r="K6" t="str">
+        <v>练习</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>